--- a/instruction/指令示例.xlsx
+++ b/instruction/指令示例.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\博士序章\博一上课程\人工智能芯片\我的部分\指令\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\intel\Downloads\TPU-Lite-SoC-main\TPU-Lite-SoC-main\instruction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACDAFCC-DDC6-41F1-96A8-42E111C865DE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455AF671-D988-4CBB-9406-1CD58DEADC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2355" uniqueCount="534">
   <si>
     <t>字段位宽</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1739,6 +1739,10 @@
   </si>
   <si>
     <t>0x3FC</t>
+  </si>
+  <si>
+    <t>00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1805,7 +1809,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1840,9 +1844,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2101,9 +2102,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{484A5EF2-7B65-4C14-96C6-EE484EE38DC4}">
   <dimension ref="A2:R375"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="3" max="18" width="11.81640625" customWidth="1"/>
+    <col min="3" max="18" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:18">
@@ -2266,13 +2267,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="16.2">
+    <row r="5" spans="1:18">
       <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>140</v>
-      </c>
+      <c r="B5" s="5"/>
       <c r="C5" s="2" t="s">
         <v>49</v>
       </c>
@@ -2288,14 +2287,14 @@
       <c r="G5" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H5" s="6">
-        <v>11</v>
+      <c r="H5" s="7" t="s">
+        <v>533</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>95</v>
       </c>
       <c r="J5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
         <v>0</v>
@@ -2322,11 +2321,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="16.2">
+    <row r="6" spans="1:18">
       <c r="A6" s="5">
         <v>2</v>
       </c>
-      <c r="B6" s="11"/>
+      <c r="B6" s="11" t="s">
+        <v>140</v>
+      </c>
       <c r="C6" s="2" t="s">
         <v>49</v>
       </c>
@@ -2334,7 +2335,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>53</v>
+        <v>333</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>114</v>
@@ -2376,7 +2377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="16.2">
+    <row r="7" spans="1:18">
       <c r="A7" s="5">
         <v>3</v>
       </c>
@@ -2388,7 +2389,7 @@
         <v>49</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>114</v>
@@ -2430,7 +2431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="16.2">
+    <row r="8" spans="1:18">
       <c r="A8" s="5">
         <v>4</v>
       </c>
@@ -2442,7 +2443,7 @@
         <v>49</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>336</v>
+        <v>57</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>114</v>
@@ -2484,7 +2485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="16.2">
+    <row r="9" spans="1:18">
       <c r="A9" s="5">
         <v>5</v>
       </c>
@@ -2496,7 +2497,7 @@
         <v>49</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>114</v>
@@ -2538,7 +2539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="16.2">
+    <row r="10" spans="1:18">
       <c r="A10" s="5">
         <v>6</v>
       </c>
@@ -2550,7 +2551,7 @@
         <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>62</v>
+        <v>334</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>114</v>
@@ -2592,7 +2593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="16.2">
+    <row r="11" spans="1:18">
       <c r="A11" s="5">
         <v>7</v>
       </c>
@@ -2604,7 +2605,7 @@
         <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>114</v>
@@ -2646,7 +2647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="16.2">
+    <row r="12" spans="1:18">
       <c r="A12" s="5">
         <v>8</v>
       </c>
@@ -2658,7 +2659,7 @@
         <v>49</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>337</v>
+        <v>66</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>114</v>
@@ -2700,7 +2701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="16.2">
+    <row r="13" spans="1:18">
       <c r="A13" s="5">
         <v>9</v>
       </c>
@@ -2712,7 +2713,7 @@
         <v>49</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>114</v>
@@ -2754,7 +2755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="16.2">
+    <row r="14" spans="1:18">
       <c r="A14" s="5">
         <v>10</v>
       </c>
@@ -2766,7 +2767,7 @@
         <v>49</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>71</v>
+        <v>335</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>114</v>
@@ -2808,7 +2809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="16.2">
+    <row r="15" spans="1:18">
       <c r="A15" s="5">
         <v>11</v>
       </c>
@@ -2820,7 +2821,7 @@
         <v>49</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>114</v>
@@ -2862,7 +2863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="16.2">
+    <row r="16" spans="1:18">
       <c r="A16" s="5">
         <v>12</v>
       </c>
@@ -2874,7 +2875,7 @@
         <v>49</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>338</v>
+        <v>75</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>114</v>
@@ -2916,7 +2917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="16.2">
+    <row r="17" spans="1:18">
       <c r="A17" s="5">
         <v>13</v>
       </c>
@@ -2928,7 +2929,7 @@
         <v>49</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>114</v>
@@ -2970,7 +2971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="16.2">
+    <row r="18" spans="1:18">
       <c r="A18" s="5">
         <v>14</v>
       </c>
@@ -2982,7 +2983,7 @@
         <v>49</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>117</v>
+        <v>339</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>114</v>
@@ -3024,7 +3025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="16.2">
+    <row r="19" spans="1:18">
       <c r="A19" s="5">
         <v>15</v>
       </c>
@@ -3036,7 +3037,7 @@
         <v>49</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>114</v>
@@ -3078,13 +3079,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="16.2">
+    <row r="20" spans="1:18">
       <c r="A20" s="5">
         <v>16</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>330</v>
-      </c>
+      <c r="B20" s="11"/>
       <c r="C20" s="2" t="s">
         <v>49</v>
       </c>
@@ -3092,7 +3091,7 @@
         <v>49</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>114</v>
@@ -3134,19 +3133,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="16.2">
+    <row r="21" spans="1:18">
       <c r="A21" s="5">
         <v>17</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="8" t="s">
+      <c r="B21" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>340</v>
+        <v>124</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>114</v>
@@ -3163,11 +3164,11 @@
       <c r="J21" s="1">
         <v>1</v>
       </c>
-      <c r="K21" s="9">
-        <v>1</v>
-      </c>
-      <c r="L21" s="9">
-        <v>1</v>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>95</v>
@@ -3188,19 +3189,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="16.2">
+    <row r="22" spans="1:18">
       <c r="A22" s="5">
         <v>18</v>
       </c>
       <c r="B22" s="11"/>
-      <c r="C22" s="2" t="s">
-        <v>50</v>
+      <c r="C22" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>130</v>
+        <v>340</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>114</v>
@@ -3217,10 +3218,10 @@
       <c r="J22" s="1">
         <v>1</v>
       </c>
-      <c r="K22" s="1">
-        <v>0</v>
-      </c>
-      <c r="L22" s="1">
+      <c r="K22" s="9">
+        <v>1</v>
+      </c>
+      <c r="L22" s="9">
         <v>1</v>
       </c>
       <c r="M22" s="7" t="s">
@@ -3242,19 +3243,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="16.2">
+    <row r="23" spans="1:18">
       <c r="A23" s="5">
         <v>19</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>114</v>
@@ -3296,19 +3297,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="16.2">
+    <row r="24" spans="1:18">
       <c r="A24" s="5">
         <v>20</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>114</v>
@@ -3350,19 +3351,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="16.2">
+    <row r="25" spans="1:18">
       <c r="A25" s="5">
         <v>21</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>114</v>
@@ -3404,19 +3405,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="16.2">
+    <row r="26" spans="1:18">
       <c r="A26" s="5">
         <v>22</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>114</v>
@@ -3458,19 +3459,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="16.2">
+    <row r="27" spans="1:18">
       <c r="A27" s="5">
         <v>23</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>114</v>
@@ -3512,19 +3513,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="16.2">
+    <row r="28" spans="1:18">
       <c r="A28" s="5">
         <v>24</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>114</v>
@@ -3566,19 +3567,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="16.2">
+    <row r="29" spans="1:18">
       <c r="A29" s="5">
         <v>25</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>114</v>
@@ -3620,19 +3621,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="16.2">
+    <row r="30" spans="1:18">
       <c r="A30" s="5">
         <v>26</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>114</v>
@@ -3674,19 +3675,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="16.2">
+    <row r="31" spans="1:18">
       <c r="A31" s="5">
         <v>27</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="2" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>114</v>
@@ -3728,19 +3729,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="16.2">
+    <row r="32" spans="1:18">
       <c r="A32" s="5">
         <v>28</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>114</v>
@@ -3782,19 +3783,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="16.2">
+    <row r="33" spans="1:18">
       <c r="A33" s="5">
         <v>29</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>114</v>
@@ -3836,19 +3837,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="16.2">
+    <row r="34" spans="1:18">
       <c r="A34" s="5">
         <v>30</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>114</v>
@@ -3890,19 +3891,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="16.2">
+    <row r="35" spans="1:18">
       <c r="A35" s="5">
         <v>31</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>114</v>
@@ -3944,19 +3945,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="16.2">
+    <row r="36" spans="1:18">
       <c r="A36" s="5">
         <v>32</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>114</v>
@@ -3979,11 +3980,11 @@
       <c r="L36" s="1">
         <v>1</v>
       </c>
-      <c r="M36" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="N36" s="9">
-        <v>0</v>
+      <c r="M36" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="N36" s="1">
+        <v>1</v>
       </c>
       <c r="O36" s="1">
         <v>0</v>
@@ -3998,19 +3999,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="16.2">
+    <row r="37" spans="1:18">
       <c r="A37" s="5">
         <v>33</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>114</v>
@@ -4027,16 +4028,16 @@
       <c r="J37" s="1">
         <v>1</v>
       </c>
-      <c r="K37" s="9">
-        <v>1</v>
+      <c r="K37" s="1">
+        <v>0</v>
       </c>
       <c r="L37" s="1">
         <v>1</v>
       </c>
-      <c r="M37" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="N37" s="1">
+      <c r="M37" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="N37" s="9">
         <v>0</v>
       </c>
       <c r="O37" s="1">
@@ -4052,19 +4053,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="16.2">
+    <row r="38" spans="1:18">
       <c r="A38" s="5">
         <v>34</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="2" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>114</v>
@@ -4081,8 +4082,8 @@
       <c r="J38" s="1">
         <v>1</v>
       </c>
-      <c r="K38" s="1">
-        <v>0</v>
+      <c r="K38" s="9">
+        <v>1</v>
       </c>
       <c r="L38" s="1">
         <v>1</v>
@@ -4106,19 +4107,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="16.2">
+    <row r="39" spans="1:18">
       <c r="A39" s="5">
         <v>35</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>114</v>
@@ -4160,19 +4161,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="16.2">
+    <row r="40" spans="1:18">
       <c r="A40" s="5">
         <v>36</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>114</v>
@@ -4214,19 +4215,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="16.2">
+    <row r="41" spans="1:18">
       <c r="A41" s="5">
         <v>37</v>
       </c>
       <c r="B41" s="11"/>
       <c r="C41" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>114</v>
@@ -4268,19 +4269,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="16.2">
+    <row r="42" spans="1:18">
       <c r="A42" s="5">
         <v>38</v>
       </c>
       <c r="B42" s="11"/>
       <c r="C42" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>114</v>
@@ -4322,19 +4323,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="16.2">
+    <row r="43" spans="1:18">
       <c r="A43" s="5">
         <v>39</v>
       </c>
       <c r="B43" s="11"/>
       <c r="C43" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>114</v>
@@ -4376,19 +4377,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="16.2">
+    <row r="44" spans="1:18">
       <c r="A44" s="5">
         <v>40</v>
       </c>
       <c r="B44" s="11"/>
       <c r="C44" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>114</v>
@@ -4430,19 +4431,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="16.2">
+    <row r="45" spans="1:18">
       <c r="A45" s="5">
         <v>41</v>
       </c>
       <c r="B45" s="11"/>
       <c r="C45" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>114</v>
@@ -4484,19 +4485,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="16.2">
+    <row r="46" spans="1:18">
       <c r="A46" s="5">
         <v>42</v>
       </c>
       <c r="B46" s="11"/>
       <c r="C46" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>114</v>
@@ -4538,19 +4539,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="16.2">
+    <row r="47" spans="1:18">
       <c r="A47" s="5">
         <v>43</v>
       </c>
       <c r="B47" s="11"/>
       <c r="C47" s="2" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>114</v>
@@ -4592,19 +4593,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="16.2">
+    <row r="48" spans="1:18">
       <c r="A48" s="5">
         <v>44</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>114</v>
@@ -4646,19 +4647,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="16.2">
+    <row r="49" spans="1:18">
       <c r="A49" s="5">
         <v>45</v>
       </c>
       <c r="B49" s="11"/>
       <c r="C49" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>114</v>
@@ -4700,19 +4701,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="16.2">
+    <row r="50" spans="1:18">
       <c r="A50" s="5">
         <v>46</v>
       </c>
       <c r="B50" s="11"/>
       <c r="C50" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>114</v>
@@ -4754,19 +4755,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="16.2">
+    <row r="51" spans="1:18">
       <c r="A51" s="5">
         <v>47</v>
       </c>
       <c r="B51" s="11"/>
       <c r="C51" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>114</v>
@@ -4808,19 +4809,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="16.2">
+    <row r="52" spans="1:18">
       <c r="A52" s="5">
         <v>48</v>
       </c>
       <c r="B52" s="11"/>
       <c r="C52" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>114</v>
@@ -4862,19 +4863,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="16.2">
+    <row r="53" spans="1:18">
       <c r="A53" s="5">
         <v>49</v>
       </c>
       <c r="B53" s="11"/>
       <c r="C53" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>114</v>
@@ -4891,8 +4892,8 @@
       <c r="J53" s="1">
         <v>1</v>
       </c>
-      <c r="K53" s="9">
-        <v>1</v>
+      <c r="K53" s="1">
+        <v>0</v>
       </c>
       <c r="L53" s="1">
         <v>1</v>
@@ -4916,19 +4917,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="16.2">
+    <row r="54" spans="1:18">
       <c r="A54" s="5">
         <v>50</v>
       </c>
       <c r="B54" s="11"/>
       <c r="C54" s="2" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>252</v>
+      <c r="E54" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>114</v>
@@ -4945,8 +4946,8 @@
       <c r="J54" s="1">
         <v>1</v>
       </c>
-      <c r="K54" s="1">
-        <v>0</v>
+      <c r="K54" s="9">
+        <v>1</v>
       </c>
       <c r="L54" s="1">
         <v>1</v>
@@ -4970,19 +4971,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="16.2">
+    <row r="55" spans="1:18">
       <c r="A55" s="5">
         <v>51</v>
       </c>
       <c r="B55" s="11"/>
       <c r="C55" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>114</v>
@@ -5024,19 +5025,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="16.2">
+    <row r="56" spans="1:18">
       <c r="A56" s="5">
         <v>52</v>
       </c>
       <c r="B56" s="11"/>
       <c r="C56" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>114</v>
@@ -5078,19 +5079,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="16.2">
+    <row r="57" spans="1:18">
       <c r="A57" s="5">
         <v>53</v>
       </c>
       <c r="B57" s="11"/>
       <c r="C57" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>114</v>
@@ -5132,19 +5133,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="16.2">
+    <row r="58" spans="1:18">
       <c r="A58" s="5">
         <v>54</v>
       </c>
       <c r="B58" s="11"/>
       <c r="C58" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>114</v>
@@ -5186,19 +5187,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="16.2">
+    <row r="59" spans="1:18">
       <c r="A59" s="5">
         <v>55</v>
       </c>
       <c r="B59" s="11"/>
       <c r="C59" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>114</v>
@@ -5240,19 +5241,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="16.2">
+    <row r="60" spans="1:18">
       <c r="A60" s="5">
         <v>56</v>
       </c>
       <c r="B60" s="11"/>
       <c r="C60" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>114</v>
@@ -5294,19 +5295,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="16.2">
+    <row r="61" spans="1:18">
       <c r="A61" s="5">
         <v>57</v>
       </c>
       <c r="B61" s="11"/>
       <c r="C61" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>114</v>
@@ -5348,19 +5349,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="16.2">
+    <row r="62" spans="1:18">
       <c r="A62" s="5">
         <v>58</v>
       </c>
       <c r="B62" s="11"/>
       <c r="C62" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>114</v>
@@ -5402,19 +5403,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="16.2">
+    <row r="63" spans="1:18">
       <c r="A63" s="5">
         <v>59</v>
       </c>
       <c r="B63" s="11"/>
       <c r="C63" s="2" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>114</v>
@@ -5456,19 +5457,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="16.2">
+    <row r="64" spans="1:18">
       <c r="A64" s="5">
         <v>60</v>
       </c>
       <c r="B64" s="11"/>
       <c r="C64" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>114</v>
@@ -5510,19 +5511,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="16.2">
+    <row r="65" spans="1:18">
       <c r="A65" s="5">
         <v>61</v>
       </c>
       <c r="B65" s="11"/>
       <c r="C65" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>114</v>
@@ -5564,19 +5565,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="16.2">
+    <row r="66" spans="1:18">
       <c r="A66" s="5">
         <v>62</v>
       </c>
       <c r="B66" s="11"/>
       <c r="C66" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>114</v>
@@ -5618,19 +5619,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="16.2">
+    <row r="67" spans="1:18">
       <c r="A67" s="5">
         <v>63</v>
       </c>
       <c r="B67" s="11"/>
       <c r="C67" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>114</v>
@@ -5672,19 +5673,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="16.2">
+    <row r="68" spans="1:18">
       <c r="A68" s="5">
         <v>64</v>
       </c>
       <c r="B68" s="11"/>
       <c r="C68" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>114</v>
@@ -5726,19 +5727,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="16.2">
+    <row r="69" spans="1:18">
       <c r="A69" s="5">
         <v>65</v>
       </c>
       <c r="B69" s="11"/>
       <c r="C69" s="2" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>341</v>
+        <v>308</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>114</v>
@@ -5755,8 +5756,8 @@
       <c r="J69" s="1">
         <v>1</v>
       </c>
-      <c r="K69" s="9">
-        <v>1</v>
+      <c r="K69" s="1">
+        <v>0</v>
       </c>
       <c r="L69" s="1">
         <v>1</v>
@@ -5780,19 +5781,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="16.2">
+    <row r="70" spans="1:18">
       <c r="A70" s="5">
         <v>66</v>
       </c>
       <c r="B70" s="11"/>
-      <c r="C70" s="1" t="s">
-        <v>77</v>
+      <c r="C70" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>114</v>
@@ -5809,8 +5810,8 @@
       <c r="J70" s="1">
         <v>1</v>
       </c>
-      <c r="K70" s="1">
-        <v>0</v>
+      <c r="K70" s="9">
+        <v>1</v>
       </c>
       <c r="L70" s="1">
         <v>1</v>
@@ -5834,19 +5835,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="16.2">
+    <row r="71" spans="1:18">
       <c r="A71" s="5">
         <v>67</v>
       </c>
       <c r="B71" s="11"/>
       <c r="C71" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>114</v>
@@ -5888,19 +5889,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="16.2">
+    <row r="72" spans="1:18">
       <c r="A72" s="5">
         <v>68</v>
       </c>
       <c r="B72" s="11"/>
       <c r="C72" s="1" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>114</v>
@@ -5942,19 +5943,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="16.2">
+    <row r="73" spans="1:18">
       <c r="A73" s="5">
         <v>69</v>
       </c>
       <c r="B73" s="11"/>
       <c r="C73" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>114</v>
@@ -5996,19 +5997,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="16.2">
+    <row r="74" spans="1:18">
       <c r="A74" s="5">
         <v>70</v>
       </c>
       <c r="B74" s="11"/>
       <c r="C74" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>114</v>
@@ -6050,19 +6051,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="16.2">
+    <row r="75" spans="1:18">
       <c r="A75" s="5">
         <v>71</v>
       </c>
       <c r="B75" s="11"/>
       <c r="C75" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>114</v>
@@ -6104,19 +6105,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="16.2">
+    <row r="76" spans="1:18">
       <c r="A76" s="5">
         <v>72</v>
       </c>
       <c r="B76" s="11"/>
       <c r="C76" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>114</v>
@@ -6158,19 +6159,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="16.2">
+    <row r="77" spans="1:18">
       <c r="A77" s="5">
         <v>73</v>
       </c>
       <c r="B77" s="11"/>
       <c r="C77" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>114</v>
@@ -6212,19 +6213,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="16.2">
+    <row r="78" spans="1:18">
       <c r="A78" s="5">
         <v>74</v>
       </c>
       <c r="B78" s="11"/>
       <c r="C78" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>114</v>
@@ -6266,19 +6267,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="16.2">
+    <row r="79" spans="1:18">
       <c r="A79" s="5">
         <v>75</v>
       </c>
       <c r="B79" s="11"/>
       <c r="C79" s="1" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>114</v>
@@ -6320,19 +6321,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="16.2">
+    <row r="80" spans="1:18">
       <c r="A80" s="5">
         <v>76</v>
       </c>
       <c r="B80" s="11"/>
       <c r="C80" s="1" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>114</v>
@@ -6374,19 +6375,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="16.2">
+    <row r="81" spans="1:18">
       <c r="A81" s="5">
         <v>77</v>
       </c>
       <c r="B81" s="11"/>
       <c r="C81" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>114</v>
@@ -6428,19 +6429,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="16.2">
+    <row r="82" spans="1:18">
       <c r="A82" s="5">
         <v>78</v>
       </c>
       <c r="B82" s="11"/>
       <c r="C82" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>114</v>
@@ -6482,19 +6483,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="16.2">
+    <row r="83" spans="1:18">
       <c r="A83" s="5">
         <v>79</v>
       </c>
       <c r="B83" s="11"/>
       <c r="C83" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>114</v>
@@ -6536,19 +6537,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="16.2">
+    <row r="84" spans="1:18">
       <c r="A84" s="5">
         <v>80</v>
       </c>
       <c r="B84" s="11"/>
       <c r="C84" s="1" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>114</v>
@@ -6590,19 +6591,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="16.2">
+    <row r="85" spans="1:18">
       <c r="A85" s="5">
         <v>81</v>
       </c>
       <c r="B85" s="11"/>
       <c r="C85" s="1" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>114</v>
@@ -6619,8 +6620,8 @@
       <c r="J85" s="1">
         <v>1</v>
       </c>
-      <c r="K85" s="9">
-        <v>1</v>
+      <c r="K85" s="1">
+        <v>0</v>
       </c>
       <c r="L85" s="1">
         <v>1</v>
@@ -6644,19 +6645,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="16.2">
+    <row r="86" spans="1:18">
       <c r="A86" s="5">
         <v>82</v>
       </c>
       <c r="B86" s="11"/>
       <c r="C86" s="1" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>114</v>
@@ -6673,8 +6674,8 @@
       <c r="J86" s="1">
         <v>1</v>
       </c>
-      <c r="K86" s="1">
-        <v>0</v>
+      <c r="K86" s="9">
+        <v>1</v>
       </c>
       <c r="L86" s="1">
         <v>1</v>
@@ -6698,19 +6699,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="16.2">
+    <row r="87" spans="1:18">
       <c r="A87" s="5">
         <v>83</v>
       </c>
       <c r="B87" s="11"/>
       <c r="C87" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>114</v>
@@ -6752,19 +6753,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="16.2">
+    <row r="88" spans="1:18">
       <c r="A88" s="5">
         <v>84</v>
       </c>
       <c r="B88" s="11"/>
       <c r="C88" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>114</v>
@@ -6806,19 +6807,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="16.2">
+    <row r="89" spans="1:18">
       <c r="A89" s="5">
         <v>85</v>
       </c>
       <c r="B89" s="11"/>
       <c r="C89" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>114</v>
@@ -6860,19 +6861,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="16.2">
+    <row r="90" spans="1:18">
       <c r="A90" s="5">
         <v>86</v>
       </c>
       <c r="B90" s="11"/>
       <c r="C90" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>114</v>
@@ -6914,19 +6915,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="16.2">
+    <row r="91" spans="1:18">
       <c r="A91" s="5">
         <v>87</v>
       </c>
       <c r="B91" s="11"/>
       <c r="C91" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>114</v>
@@ -6968,19 +6969,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="16.2">
+    <row r="92" spans="1:18">
       <c r="A92" s="5">
         <v>88</v>
       </c>
       <c r="B92" s="11"/>
       <c r="C92" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>114</v>
@@ -7022,19 +7023,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="16.2">
+    <row r="93" spans="1:18">
       <c r="A93" s="5">
         <v>89</v>
       </c>
       <c r="B93" s="11"/>
       <c r="C93" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>114</v>
@@ -7076,19 +7077,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="16.2">
+    <row r="94" spans="1:18">
       <c r="A94" s="5">
         <v>90</v>
       </c>
       <c r="B94" s="11"/>
       <c r="C94" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>114</v>
@@ -7130,19 +7131,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="16.2">
+    <row r="95" spans="1:18">
       <c r="A95" s="5">
         <v>91</v>
       </c>
       <c r="B95" s="11"/>
       <c r="C95" s="1" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>114</v>
@@ -7184,19 +7185,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="16.2">
+    <row r="96" spans="1:18">
       <c r="A96" s="5">
         <v>92</v>
       </c>
       <c r="B96" s="11"/>
       <c r="C96" s="1" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>114</v>
@@ -7238,19 +7239,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="16.2">
+    <row r="97" spans="1:18">
       <c r="A97" s="5">
         <v>93</v>
       </c>
       <c r="B97" s="11"/>
       <c r="C97" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>114</v>
@@ -7292,19 +7293,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="16.2">
+    <row r="98" spans="1:18">
       <c r="A98" s="5">
         <v>94</v>
       </c>
       <c r="B98" s="11"/>
       <c r="C98" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>114</v>
@@ -7346,19 +7347,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="16.2">
+    <row r="99" spans="1:18">
       <c r="A99" s="5">
         <v>95</v>
       </c>
       <c r="B99" s="11"/>
       <c r="C99" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>114</v>
@@ -7400,19 +7401,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="16.2">
+    <row r="100" spans="1:18">
       <c r="A100" s="5">
         <v>96</v>
       </c>
       <c r="B100" s="11"/>
       <c r="C100" s="1" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>114</v>
@@ -7454,19 +7455,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="16.2">
+    <row r="101" spans="1:18">
       <c r="A101" s="5">
         <v>97</v>
       </c>
       <c r="B101" s="11"/>
       <c r="C101" s="1" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>114</v>
@@ -7483,8 +7484,8 @@
       <c r="J101" s="1">
         <v>1</v>
       </c>
-      <c r="K101" s="9">
-        <v>1</v>
+      <c r="K101" s="1">
+        <v>0</v>
       </c>
       <c r="L101" s="1">
         <v>1</v>
@@ -7508,19 +7509,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="16.2">
+    <row r="102" spans="1:18">
       <c r="A102" s="5">
         <v>98</v>
       </c>
       <c r="B102" s="11"/>
       <c r="C102" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>114</v>
@@ -7537,8 +7538,8 @@
       <c r="J102" s="1">
         <v>1</v>
       </c>
-      <c r="K102" s="1">
-        <v>0</v>
+      <c r="K102" s="9">
+        <v>1</v>
       </c>
       <c r="L102" s="1">
         <v>1</v>
@@ -7562,19 +7563,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="16.2">
+    <row r="103" spans="1:18">
       <c r="A103" s="5">
         <v>99</v>
       </c>
       <c r="B103" s="11"/>
       <c r="C103" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>114</v>
@@ -7616,19 +7617,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="16.2">
+    <row r="104" spans="1:18">
       <c r="A104" s="5">
         <v>100</v>
       </c>
       <c r="B104" s="11"/>
       <c r="C104" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>114</v>
@@ -7670,19 +7671,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="16.2">
+    <row r="105" spans="1:18">
       <c r="A105" s="5">
         <v>101</v>
       </c>
       <c r="B105" s="11"/>
       <c r="C105" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>114</v>
@@ -7724,19 +7725,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="16.2">
+    <row r="106" spans="1:18">
       <c r="A106" s="5">
         <v>102</v>
       </c>
       <c r="B106" s="11"/>
       <c r="C106" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>114</v>
@@ -7778,19 +7779,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="16.2">
+    <row r="107" spans="1:18">
       <c r="A107" s="5">
         <v>103</v>
       </c>
       <c r="B107" s="11"/>
       <c r="C107" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>114</v>
@@ -7832,19 +7833,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="16.2">
+    <row r="108" spans="1:18">
       <c r="A108" s="5">
         <v>104</v>
       </c>
       <c r="B108" s="11"/>
       <c r="C108" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>114</v>
@@ -7886,19 +7887,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="16.2">
+    <row r="109" spans="1:18">
       <c r="A109" s="5">
         <v>105</v>
       </c>
       <c r="B109" s="11"/>
       <c r="C109" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>114</v>
@@ -7940,19 +7941,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="16.2">
+    <row r="110" spans="1:18">
       <c r="A110" s="5">
         <v>106</v>
       </c>
       <c r="B110" s="11"/>
       <c r="C110" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>114</v>
@@ -7994,19 +7995,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="16.2">
+    <row r="111" spans="1:18">
       <c r="A111" s="5">
         <v>107</v>
       </c>
       <c r="B111" s="11"/>
       <c r="C111" s="1" t="s">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>114</v>
@@ -8048,19 +8049,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="16.2">
+    <row r="112" spans="1:18">
       <c r="A112" s="5">
         <v>108</v>
       </c>
       <c r="B112" s="11"/>
       <c r="C112" s="1" t="s">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>114</v>
@@ -8102,19 +8103,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="16.2">
+    <row r="113" spans="1:18">
       <c r="A113" s="5">
         <v>109</v>
       </c>
       <c r="B113" s="11"/>
       <c r="C113" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>114</v>
@@ -8156,19 +8157,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="16.2">
+    <row r="114" spans="1:18">
       <c r="A114" s="5">
         <v>110</v>
       </c>
       <c r="B114" s="11"/>
       <c r="C114" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>114</v>
@@ -8210,19 +8211,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="16.2">
+    <row r="115" spans="1:18">
       <c r="A115" s="5">
         <v>111</v>
       </c>
       <c r="B115" s="11"/>
       <c r="C115" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>114</v>
@@ -8264,19 +8265,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="16.2">
+    <row r="116" spans="1:18">
       <c r="A116" s="5">
         <v>112</v>
       </c>
       <c r="B116" s="11"/>
       <c r="C116" s="1" t="s">
-        <v>98</v>
+        <v>157</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>114</v>
@@ -8318,19 +8319,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="16.2">
+    <row r="117" spans="1:18">
       <c r="A117" s="5">
         <v>113</v>
       </c>
       <c r="B117" s="11"/>
       <c r="C117" s="1" t="s">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>114</v>
@@ -8347,8 +8348,8 @@
       <c r="J117" s="1">
         <v>1</v>
       </c>
-      <c r="K117" s="9">
-        <v>1</v>
+      <c r="K117" s="1">
+        <v>0</v>
       </c>
       <c r="L117" s="1">
         <v>1</v>
@@ -8372,19 +8373,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="16.2">
+    <row r="118" spans="1:18">
       <c r="A118" s="5">
         <v>114</v>
       </c>
       <c r="B118" s="11"/>
       <c r="C118" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>114</v>
@@ -8401,8 +8402,8 @@
       <c r="J118" s="1">
         <v>1</v>
       </c>
-      <c r="K118" s="1">
-        <v>0</v>
+      <c r="K118" s="9">
+        <v>1</v>
       </c>
       <c r="L118" s="1">
         <v>1</v>
@@ -8426,19 +8427,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="16.2">
+    <row r="119" spans="1:18">
       <c r="A119" s="5">
         <v>115</v>
       </c>
       <c r="B119" s="11"/>
       <c r="C119" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>114</v>
@@ -8480,19 +8481,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="16.2">
+    <row r="120" spans="1:18">
       <c r="A120" s="5">
         <v>116</v>
       </c>
       <c r="B120" s="11"/>
       <c r="C120" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>114</v>
@@ -8534,19 +8535,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="16.2">
+    <row r="121" spans="1:18">
       <c r="A121" s="5">
         <v>117</v>
       </c>
       <c r="B121" s="11"/>
       <c r="C121" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>114</v>
@@ -8588,19 +8589,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="16.2">
+    <row r="122" spans="1:18">
       <c r="A122" s="5">
         <v>118</v>
       </c>
       <c r="B122" s="11"/>
       <c r="C122" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>114</v>
@@ -8642,19 +8643,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="16.2">
+    <row r="123" spans="1:18">
       <c r="A123" s="5">
         <v>119</v>
       </c>
       <c r="B123" s="11"/>
       <c r="C123" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>114</v>
@@ -8696,19 +8697,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="16.2">
+    <row r="124" spans="1:18">
       <c r="A124" s="5">
         <v>120</v>
       </c>
       <c r="B124" s="11"/>
       <c r="C124" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>114</v>
@@ -8750,19 +8751,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="16.2">
+    <row r="125" spans="1:18">
       <c r="A125" s="5">
         <v>121</v>
       </c>
       <c r="B125" s="11"/>
       <c r="C125" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>114</v>
@@ -8804,19 +8805,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="16.2">
+    <row r="126" spans="1:18">
       <c r="A126" s="5">
         <v>122</v>
       </c>
       <c r="B126" s="11"/>
       <c r="C126" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>114</v>
@@ -8858,19 +8859,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="16.2">
+    <row r="127" spans="1:18">
       <c r="A127" s="5">
         <v>123</v>
       </c>
       <c r="B127" s="11"/>
       <c r="C127" s="1" t="s">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>114</v>
@@ -8912,19 +8913,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="16.2">
+    <row r="128" spans="1:18">
       <c r="A128" s="5">
         <v>124</v>
       </c>
       <c r="B128" s="11"/>
       <c r="C128" s="1" t="s">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>114</v>
@@ -8966,19 +8967,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="16.2">
+    <row r="129" spans="1:18">
       <c r="A129" s="5">
         <v>125</v>
       </c>
       <c r="B129" s="11"/>
       <c r="C129" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>114</v>
@@ -9020,19 +9021,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="16.2">
+    <row r="130" spans="1:18">
       <c r="A130" s="5">
         <v>126</v>
       </c>
       <c r="B130" s="11"/>
       <c r="C130" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>114</v>
@@ -9074,19 +9075,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="16.2">
+    <row r="131" spans="1:18">
       <c r="A131" s="5">
         <v>127</v>
       </c>
       <c r="B131" s="11"/>
       <c r="C131" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>114</v>
@@ -9128,19 +9129,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="16.2">
+    <row r="132" spans="1:18">
       <c r="A132" s="5">
         <v>128</v>
       </c>
       <c r="B132" s="11"/>
       <c r="C132" s="1" t="s">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>114</v>
@@ -9182,19 +9183,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="16.2">
+    <row r="133" spans="1:18">
       <c r="A133" s="5">
         <v>129</v>
       </c>
       <c r="B133" s="11"/>
       <c r="C133" s="1" t="s">
-        <v>172</v>
+        <v>99</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E133" s="2" t="s">
-        <v>468</v>
+      <c r="E133" s="1" t="s">
+        <v>404</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>114</v>
@@ -9211,8 +9212,8 @@
       <c r="J133" s="1">
         <v>1</v>
       </c>
-      <c r="K133" s="9">
-        <v>1</v>
+      <c r="K133" s="1">
+        <v>0</v>
       </c>
       <c r="L133" s="1">
         <v>1</v>
@@ -9236,19 +9237,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="16.2">
+    <row r="134" spans="1:18">
       <c r="A134" s="5">
         <v>130</v>
       </c>
       <c r="B134" s="11"/>
       <c r="C134" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E134" s="1" t="s">
-        <v>405</v>
+      <c r="E134" s="2" t="s">
+        <v>468</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>114</v>
@@ -9265,8 +9266,8 @@
       <c r="J134" s="1">
         <v>1</v>
       </c>
-      <c r="K134" s="1">
-        <v>0</v>
+      <c r="K134" s="9">
+        <v>1</v>
       </c>
       <c r="L134" s="1">
         <v>1</v>
@@ -9290,19 +9291,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="16.2">
+    <row r="135" spans="1:18">
       <c r="A135" s="5">
         <v>131</v>
       </c>
       <c r="B135" s="11"/>
       <c r="C135" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>114</v>
@@ -9344,19 +9345,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="16.2">
+    <row r="136" spans="1:18">
       <c r="A136" s="5">
         <v>132</v>
       </c>
       <c r="B136" s="11"/>
       <c r="C136" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>114</v>
@@ -9398,19 +9399,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="16.2">
+    <row r="137" spans="1:18">
       <c r="A137" s="5">
         <v>133</v>
       </c>
       <c r="B137" s="11"/>
       <c r="C137" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>114</v>
@@ -9452,19 +9453,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="16.2">
+    <row r="138" spans="1:18">
       <c r="A138" s="5">
         <v>134</v>
       </c>
       <c r="B138" s="11"/>
       <c r="C138" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>114</v>
@@ -9506,19 +9507,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="16.2">
+    <row r="139" spans="1:18">
       <c r="A139" s="5">
         <v>135</v>
       </c>
       <c r="B139" s="11"/>
       <c r="C139" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>114</v>
@@ -9560,19 +9561,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="16.2">
+    <row r="140" spans="1:18">
       <c r="A140" s="5">
         <v>136</v>
       </c>
       <c r="B140" s="11"/>
       <c r="C140" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>114</v>
@@ -9614,19 +9615,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="16.2">
+    <row r="141" spans="1:18">
       <c r="A141" s="5">
         <v>137</v>
       </c>
       <c r="B141" s="11"/>
       <c r="C141" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>114</v>
@@ -9668,19 +9669,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="16.2">
+    <row r="142" spans="1:18">
       <c r="A142" s="5">
         <v>138</v>
       </c>
       <c r="B142" s="11"/>
       <c r="C142" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>114</v>
@@ -9722,19 +9723,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="16.2">
+    <row r="143" spans="1:18">
       <c r="A143" s="5">
         <v>139</v>
       </c>
       <c r="B143" s="11"/>
       <c r="C143" s="1" t="s">
-        <v>109</v>
+        <v>181</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>114</v>
@@ -9776,19 +9777,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="16.2">
+    <row r="144" spans="1:18">
       <c r="A144" s="5">
         <v>140</v>
       </c>
       <c r="B144" s="11"/>
       <c r="C144" s="1" t="s">
-        <v>182</v>
+        <v>109</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>114</v>
@@ -9830,19 +9831,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="16.2">
+    <row r="145" spans="1:18">
       <c r="A145" s="5">
         <v>141</v>
       </c>
       <c r="B145" s="11"/>
       <c r="C145" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>114</v>
@@ -9884,19 +9885,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="16.2">
+    <row r="146" spans="1:18">
       <c r="A146" s="5">
         <v>142</v>
       </c>
       <c r="B146" s="11"/>
       <c r="C146" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>114</v>
@@ -9938,19 +9939,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="16.2">
+    <row r="147" spans="1:18">
       <c r="A147" s="5">
         <v>143</v>
       </c>
       <c r="B147" s="11"/>
       <c r="C147" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>114</v>
@@ -9992,19 +9993,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="16.2">
+    <row r="148" spans="1:18">
       <c r="A148" s="5">
         <v>144</v>
       </c>
       <c r="B148" s="11"/>
       <c r="C148" s="1" t="s">
-        <v>100</v>
+        <v>185</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>114</v>
@@ -10046,19 +10047,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="16.2">
+    <row r="149" spans="1:18">
       <c r="A149" s="5">
         <v>145</v>
       </c>
       <c r="B149" s="11"/>
       <c r="C149" s="1" t="s">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>114</v>
@@ -10075,8 +10076,8 @@
       <c r="J149" s="1">
         <v>1</v>
       </c>
-      <c r="K149" s="9">
-        <v>1</v>
+      <c r="K149" s="1">
+        <v>0</v>
       </c>
       <c r="L149" s="1">
         <v>1</v>
@@ -10100,19 +10101,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="16.2">
+    <row r="150" spans="1:18">
       <c r="A150" s="5">
         <v>146</v>
       </c>
       <c r="B150" s="11"/>
       <c r="C150" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>114</v>
@@ -10129,8 +10130,8 @@
       <c r="J150" s="1">
         <v>1</v>
       </c>
-      <c r="K150" s="1">
-        <v>0</v>
+      <c r="K150" s="9">
+        <v>1</v>
       </c>
       <c r="L150" s="1">
         <v>1</v>
@@ -10154,19 +10155,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="16.2">
+    <row r="151" spans="1:18">
       <c r="A151" s="5">
         <v>147</v>
       </c>
       <c r="B151" s="11"/>
       <c r="C151" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>114</v>
@@ -10208,19 +10209,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="16.2">
+    <row r="152" spans="1:18">
       <c r="A152" s="5">
         <v>148</v>
       </c>
       <c r="B152" s="11"/>
       <c r="C152" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>114</v>
@@ -10262,19 +10263,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="16.2">
+    <row r="153" spans="1:18">
       <c r="A153" s="5">
         <v>149</v>
       </c>
       <c r="B153" s="11"/>
       <c r="C153" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>114</v>
@@ -10316,19 +10317,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="16.2">
+    <row r="154" spans="1:18">
       <c r="A154" s="5">
         <v>150</v>
       </c>
       <c r="B154" s="11"/>
       <c r="C154" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>114</v>
@@ -10370,19 +10371,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="16.2">
+    <row r="155" spans="1:18">
       <c r="A155" s="5">
         <v>151</v>
       </c>
       <c r="B155" s="11"/>
       <c r="C155" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>114</v>
@@ -10424,19 +10425,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="16.2">
+    <row r="156" spans="1:18">
       <c r="A156" s="5">
         <v>152</v>
       </c>
       <c r="B156" s="11"/>
       <c r="C156" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>114</v>
@@ -10478,19 +10479,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="16.2">
+    <row r="157" spans="1:18">
       <c r="A157" s="5">
         <v>153</v>
       </c>
       <c r="B157" s="11"/>
       <c r="C157" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>114</v>
@@ -10532,19 +10533,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="16.2">
+    <row r="158" spans="1:18">
       <c r="A158" s="5">
         <v>154</v>
       </c>
       <c r="B158" s="11"/>
       <c r="C158" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>114</v>
@@ -10586,19 +10587,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="16.2">
+    <row r="159" spans="1:18">
       <c r="A159" s="5">
         <v>155</v>
       </c>
       <c r="B159" s="11"/>
       <c r="C159" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>114</v>
@@ -10640,19 +10641,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="16.2">
+    <row r="160" spans="1:18">
       <c r="A160" s="5">
         <v>156</v>
       </c>
       <c r="B160" s="11"/>
       <c r="C160" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>114</v>
@@ -10694,19 +10695,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="16.2">
+    <row r="161" spans="1:18">
       <c r="A161" s="5">
         <v>157</v>
       </c>
       <c r="B161" s="11"/>
       <c r="C161" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>114</v>
@@ -10748,19 +10749,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="16.2">
+    <row r="162" spans="1:18">
       <c r="A162" s="5">
         <v>158</v>
       </c>
       <c r="B162" s="11"/>
       <c r="C162" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>114</v>
@@ -10802,19 +10803,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="16.2">
+    <row r="163" spans="1:18">
       <c r="A163" s="5">
         <v>159</v>
       </c>
       <c r="B163" s="11"/>
       <c r="C163" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>114</v>
@@ -10856,19 +10857,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="16.2">
+    <row r="164" spans="1:18">
       <c r="A164" s="5">
         <v>160</v>
       </c>
       <c r="B164" s="11"/>
       <c r="C164" s="1" t="s">
-        <v>101</v>
+        <v>200</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>114</v>
@@ -10910,19 +10911,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="16.2">
+    <row r="165" spans="1:18">
       <c r="A165" s="5">
         <v>161</v>
       </c>
       <c r="B165" s="11"/>
       <c r="C165" s="1" t="s">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>114</v>
@@ -10939,8 +10940,8 @@
       <c r="J165" s="1">
         <v>1</v>
       </c>
-      <c r="K165" s="9">
-        <v>1</v>
+      <c r="K165" s="1">
+        <v>0</v>
       </c>
       <c r="L165" s="1">
         <v>1</v>
@@ -10964,19 +10965,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="16.2">
+    <row r="166" spans="1:18">
       <c r="A166" s="5">
         <v>162</v>
       </c>
       <c r="B166" s="11"/>
       <c r="C166" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>114</v>
@@ -10993,8 +10994,8 @@
       <c r="J166" s="1">
         <v>1</v>
       </c>
-      <c r="K166" s="1">
-        <v>0</v>
+      <c r="K166" s="9">
+        <v>1</v>
       </c>
       <c r="L166" s="1">
         <v>1</v>
@@ -11018,19 +11019,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="16.2">
+    <row r="167" spans="1:18">
       <c r="A167" s="5">
         <v>163</v>
       </c>
       <c r="B167" s="11"/>
       <c r="C167" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>114</v>
@@ -11072,19 +11073,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="16.2">
+    <row r="168" spans="1:18">
       <c r="A168" s="5">
         <v>164</v>
       </c>
       <c r="B168" s="11"/>
       <c r="C168" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>114</v>
@@ -11126,19 +11127,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="16.2">
+    <row r="169" spans="1:18">
       <c r="A169" s="5">
         <v>165</v>
       </c>
       <c r="B169" s="11"/>
       <c r="C169" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>114</v>
@@ -11180,19 +11181,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="16.2">
+    <row r="170" spans="1:18">
       <c r="A170" s="5">
         <v>166</v>
       </c>
       <c r="B170" s="11"/>
       <c r="C170" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>114</v>
@@ -11234,19 +11235,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="16.2">
+    <row r="171" spans="1:18">
       <c r="A171" s="5">
         <v>167</v>
       </c>
       <c r="B171" s="11"/>
       <c r="C171" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>114</v>
@@ -11288,19 +11289,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="16.2">
+    <row r="172" spans="1:18">
       <c r="A172" s="5">
         <v>168</v>
       </c>
       <c r="B172" s="11"/>
       <c r="C172" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>114</v>
@@ -11342,19 +11343,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="16.2">
+    <row r="173" spans="1:18">
       <c r="A173" s="5">
         <v>169</v>
       </c>
       <c r="B173" s="11"/>
       <c r="C173" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>114</v>
@@ -11396,19 +11397,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="16.2">
+    <row r="174" spans="1:18">
       <c r="A174" s="5">
         <v>170</v>
       </c>
       <c r="B174" s="11"/>
       <c r="C174" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>114</v>
@@ -11450,19 +11451,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="16.2">
+    <row r="175" spans="1:18">
       <c r="A175" s="5">
         <v>171</v>
       </c>
       <c r="B175" s="11"/>
       <c r="C175" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>114</v>
@@ -11504,19 +11505,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="16.2">
+    <row r="176" spans="1:18">
       <c r="A176" s="5">
         <v>172</v>
       </c>
       <c r="B176" s="11"/>
       <c r="C176" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>114</v>
@@ -11558,19 +11559,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="16.2">
+    <row r="177" spans="1:18">
       <c r="A177" s="5">
         <v>173</v>
       </c>
       <c r="B177" s="11"/>
       <c r="C177" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>114</v>
@@ -11612,19 +11613,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="16.2">
+    <row r="178" spans="1:18">
       <c r="A178" s="5">
         <v>174</v>
       </c>
       <c r="B178" s="11"/>
       <c r="C178" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>114</v>
@@ -11666,19 +11667,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="16.2">
+    <row r="179" spans="1:18">
       <c r="A179" s="5">
         <v>175</v>
       </c>
       <c r="B179" s="11"/>
       <c r="C179" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>114</v>
@@ -11720,19 +11721,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="16.2">
+    <row r="180" spans="1:18">
       <c r="A180" s="5">
         <v>176</v>
       </c>
       <c r="B180" s="11"/>
       <c r="C180" s="1" t="s">
-        <v>102</v>
+        <v>215</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F180" s="2" t="s">
         <v>114</v>
@@ -11774,19 +11775,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="16.2">
+    <row r="181" spans="1:18">
       <c r="A181" s="5">
         <v>177</v>
       </c>
       <c r="B181" s="11"/>
       <c r="C181" s="1" t="s">
-        <v>216</v>
+        <v>102</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>114</v>
@@ -11803,8 +11804,8 @@
       <c r="J181" s="1">
         <v>1</v>
       </c>
-      <c r="K181" s="9">
-        <v>1</v>
+      <c r="K181" s="1">
+        <v>0</v>
       </c>
       <c r="L181" s="1">
         <v>1</v>
@@ -11828,19 +11829,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="16.2">
+    <row r="182" spans="1:18">
       <c r="A182" s="5">
         <v>178</v>
       </c>
       <c r="B182" s="11"/>
       <c r="C182" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>114</v>
@@ -11857,8 +11858,8 @@
       <c r="J182" s="1">
         <v>1</v>
       </c>
-      <c r="K182" s="1">
-        <v>0</v>
+      <c r="K182" s="9">
+        <v>1</v>
       </c>
       <c r="L182" s="1">
         <v>1</v>
@@ -11882,19 +11883,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="16.2">
+    <row r="183" spans="1:18">
       <c r="A183" s="5">
         <v>179</v>
       </c>
       <c r="B183" s="11"/>
       <c r="C183" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>114</v>
@@ -11936,19 +11937,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="16.2">
+    <row r="184" spans="1:18">
       <c r="A184" s="5">
         <v>180</v>
       </c>
       <c r="B184" s="11"/>
       <c r="C184" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>114</v>
@@ -11990,19 +11991,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="16.2">
+    <row r="185" spans="1:18">
       <c r="A185" s="5">
         <v>181</v>
       </c>
       <c r="B185" s="11"/>
       <c r="C185" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>114</v>
@@ -12044,19 +12045,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="16.2">
+    <row r="186" spans="1:18">
       <c r="A186" s="5">
         <v>182</v>
       </c>
       <c r="B186" s="11"/>
       <c r="C186" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>114</v>
@@ -12098,19 +12099,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="16.2">
+    <row r="187" spans="1:18">
       <c r="A187" s="5">
         <v>183</v>
       </c>
       <c r="B187" s="11"/>
       <c r="C187" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>114</v>
@@ -12152,19 +12153,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="16.2">
+    <row r="188" spans="1:18">
       <c r="A188" s="5">
         <v>184</v>
       </c>
       <c r="B188" s="11"/>
       <c r="C188" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F188" s="2" t="s">
         <v>114</v>
@@ -12206,19 +12207,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="16.2">
+    <row r="189" spans="1:18">
       <c r="A189" s="5">
         <v>185</v>
       </c>
       <c r="B189" s="11"/>
       <c r="C189" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>114</v>
@@ -12260,19 +12261,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="16.2">
+    <row r="190" spans="1:18">
       <c r="A190" s="5">
         <v>186</v>
       </c>
       <c r="B190" s="11"/>
       <c r="C190" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>114</v>
@@ -12314,19 +12315,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="16.2">
+    <row r="191" spans="1:18">
       <c r="A191" s="5">
         <v>187</v>
       </c>
       <c r="B191" s="11"/>
       <c r="C191" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>114</v>
@@ -12368,19 +12369,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="16.2">
+    <row r="192" spans="1:18">
       <c r="A192" s="5">
         <v>188</v>
       </c>
       <c r="B192" s="11"/>
       <c r="C192" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>114</v>
@@ -12422,19 +12423,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="16.2">
+    <row r="193" spans="1:18">
       <c r="A193" s="5">
         <v>189</v>
       </c>
       <c r="B193" s="11"/>
       <c r="C193" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>114</v>
@@ -12476,19 +12477,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="16.2">
+    <row r="194" spans="1:18">
       <c r="A194" s="5">
         <v>190</v>
       </c>
       <c r="B194" s="11"/>
       <c r="C194" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>114</v>
@@ -12530,19 +12531,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="16.2">
+    <row r="195" spans="1:18">
       <c r="A195" s="5">
         <v>191</v>
       </c>
       <c r="B195" s="11"/>
       <c r="C195" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>114</v>
@@ -12584,19 +12585,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="16.2">
+    <row r="196" spans="1:18">
       <c r="A196" s="5">
         <v>192</v>
       </c>
       <c r="B196" s="11"/>
       <c r="C196" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>114</v>
@@ -12638,19 +12639,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="16.2">
+    <row r="197" spans="1:18">
       <c r="A197" s="5">
         <v>193</v>
       </c>
       <c r="B197" s="11"/>
       <c r="C197" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>114</v>
@@ -12667,8 +12668,8 @@
       <c r="J197" s="1">
         <v>1</v>
       </c>
-      <c r="K197" s="9">
-        <v>1</v>
+      <c r="K197" s="1">
+        <v>0</v>
       </c>
       <c r="L197" s="1">
         <v>1</v>
@@ -12692,19 +12693,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="16.2">
+    <row r="198" spans="1:18">
       <c r="A198" s="5">
         <v>194</v>
       </c>
       <c r="B198" s="11"/>
       <c r="C198" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>114</v>
@@ -12721,8 +12722,8 @@
       <c r="J198" s="1">
         <v>1</v>
       </c>
-      <c r="K198" s="1">
-        <v>0</v>
+      <c r="K198" s="9">
+        <v>1</v>
       </c>
       <c r="L198" s="1">
         <v>1</v>
@@ -12746,19 +12747,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="16.2">
+    <row r="199" spans="1:18">
       <c r="A199" s="5">
         <v>195</v>
       </c>
       <c r="B199" s="11"/>
       <c r="C199" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>114</v>
@@ -12800,19 +12801,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="16.2">
+    <row r="200" spans="1:18">
       <c r="A200" s="5">
         <v>196</v>
       </c>
       <c r="B200" s="11"/>
       <c r="C200" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>114</v>
@@ -12854,19 +12855,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="16.2">
+    <row r="201" spans="1:18">
       <c r="A201" s="5">
         <v>197</v>
       </c>
       <c r="B201" s="11"/>
       <c r="C201" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>114</v>
@@ -12908,19 +12909,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="16.2">
+    <row r="202" spans="1:18">
       <c r="A202" s="5">
         <v>198</v>
       </c>
       <c r="B202" s="11"/>
       <c r="C202" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>114</v>
@@ -12962,19 +12963,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="16.2">
+    <row r="203" spans="1:18">
       <c r="A203" s="5">
         <v>199</v>
       </c>
       <c r="B203" s="11"/>
       <c r="C203" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>114</v>
@@ -13016,19 +13017,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="16.2">
+    <row r="204" spans="1:18">
       <c r="A204" s="5">
         <v>200</v>
       </c>
       <c r="B204" s="11"/>
       <c r="C204" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>114</v>
@@ -13070,19 +13071,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="16.2">
+    <row r="205" spans="1:18">
       <c r="A205" s="5">
         <v>201</v>
       </c>
       <c r="B205" s="11"/>
       <c r="C205" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>114</v>
@@ -13124,19 +13125,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="16.2">
+    <row r="206" spans="1:18">
       <c r="A206" s="5">
         <v>202</v>
       </c>
       <c r="B206" s="11"/>
       <c r="C206" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>114</v>
@@ -13178,19 +13179,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="16.2">
+    <row r="207" spans="1:18">
       <c r="A207" s="5">
         <v>203</v>
       </c>
       <c r="B207" s="11"/>
       <c r="C207" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>114</v>
@@ -13232,19 +13233,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="16.2">
+    <row r="208" spans="1:18">
       <c r="A208" s="5">
         <v>204</v>
       </c>
       <c r="B208" s="11"/>
       <c r="C208" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>114</v>
@@ -13286,19 +13287,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="16.2">
+    <row r="209" spans="1:18">
       <c r="A209" s="5">
         <v>205</v>
       </c>
       <c r="B209" s="11"/>
       <c r="C209" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>114</v>
@@ -13340,19 +13341,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="16.2">
+    <row r="210" spans="1:18">
       <c r="A210" s="5">
         <v>206</v>
       </c>
       <c r="B210" s="11"/>
       <c r="C210" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>114</v>
@@ -13394,19 +13395,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="16.2">
+    <row r="211" spans="1:18">
       <c r="A211" s="5">
         <v>207</v>
       </c>
       <c r="B211" s="11"/>
       <c r="C211" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>114</v>
@@ -13448,19 +13449,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="16.2">
+    <row r="212" spans="1:18">
       <c r="A212" s="5">
         <v>208</v>
       </c>
       <c r="B212" s="11"/>
       <c r="C212" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>114</v>
@@ -13502,19 +13503,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="16.2">
+    <row r="213" spans="1:18">
       <c r="A213" s="5">
         <v>209</v>
       </c>
       <c r="B213" s="11"/>
       <c r="C213" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>114</v>
@@ -13531,8 +13532,8 @@
       <c r="J213" s="1">
         <v>1</v>
       </c>
-      <c r="K213" s="9">
-        <v>1</v>
+      <c r="K213" s="1">
+        <v>0</v>
       </c>
       <c r="L213" s="1">
         <v>1</v>
@@ -13556,19 +13557,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="16.2">
+    <row r="214" spans="1:18">
       <c r="A214" s="5">
         <v>210</v>
       </c>
       <c r="B214" s="11"/>
       <c r="C214" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>114</v>
@@ -13585,8 +13586,8 @@
       <c r="J214" s="1">
         <v>1</v>
       </c>
-      <c r="K214" s="1">
-        <v>0</v>
+      <c r="K214" s="9">
+        <v>1</v>
       </c>
       <c r="L214" s="1">
         <v>1</v>
@@ -13610,19 +13611,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="16.2">
+    <row r="215" spans="1:18">
       <c r="A215" s="5">
         <v>211</v>
       </c>
       <c r="B215" s="11"/>
       <c r="C215" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>114</v>
@@ -13664,19 +13665,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="16.2">
+    <row r="216" spans="1:18">
       <c r="A216" s="5">
         <v>212</v>
       </c>
       <c r="B216" s="11"/>
       <c r="C216" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>114</v>
@@ -13718,19 +13719,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="16.2">
+    <row r="217" spans="1:18">
       <c r="A217" s="5">
         <v>213</v>
       </c>
       <c r="B217" s="11"/>
       <c r="C217" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>114</v>
@@ -13772,19 +13773,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="16.2">
+    <row r="218" spans="1:18">
       <c r="A218" s="5">
         <v>214</v>
       </c>
       <c r="B218" s="11"/>
       <c r="C218" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>114</v>
@@ -13826,19 +13827,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="16.2">
+    <row r="219" spans="1:18">
       <c r="A219" s="5">
         <v>215</v>
       </c>
       <c r="B219" s="11"/>
       <c r="C219" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>114</v>
@@ -13880,19 +13881,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="16.2">
+    <row r="220" spans="1:18">
       <c r="A220" s="5">
         <v>216</v>
       </c>
       <c r="B220" s="11"/>
       <c r="C220" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F220" s="2" t="s">
         <v>114</v>
@@ -13934,19 +13935,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="16.2">
+    <row r="221" spans="1:18">
       <c r="A221" s="5">
         <v>217</v>
       </c>
       <c r="B221" s="11"/>
       <c r="C221" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F221" s="2" t="s">
         <v>114</v>
@@ -13988,19 +13989,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="16.2">
+    <row r="222" spans="1:18">
       <c r="A222" s="5">
         <v>218</v>
       </c>
       <c r="B222" s="11"/>
       <c r="C222" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>114</v>
@@ -14042,19 +14043,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="16.2">
+    <row r="223" spans="1:18">
       <c r="A223" s="5">
         <v>219</v>
       </c>
       <c r="B223" s="11"/>
       <c r="C223" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>114</v>
@@ -14096,19 +14097,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="16.2">
+    <row r="224" spans="1:18">
       <c r="A224" s="5">
         <v>220</v>
       </c>
       <c r="B224" s="11"/>
       <c r="C224" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>114</v>
@@ -14150,19 +14151,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="16.2">
+    <row r="225" spans="1:18">
       <c r="A225" s="5">
         <v>221</v>
       </c>
       <c r="B225" s="11"/>
       <c r="C225" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>114</v>
@@ -14204,19 +14205,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="16.2">
+    <row r="226" spans="1:18">
       <c r="A226" s="5">
         <v>222</v>
       </c>
       <c r="B226" s="11"/>
       <c r="C226" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>114</v>
@@ -14258,19 +14259,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="16.2">
+    <row r="227" spans="1:18">
       <c r="A227" s="5">
         <v>223</v>
       </c>
       <c r="B227" s="11"/>
       <c r="C227" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>114</v>
@@ -14312,19 +14313,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="16.2">
+    <row r="228" spans="1:18">
       <c r="A228" s="5">
         <v>224</v>
       </c>
       <c r="B228" s="11"/>
       <c r="C228" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>114</v>
@@ -14366,19 +14367,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="16.2">
+    <row r="229" spans="1:18">
       <c r="A229" s="5">
         <v>225</v>
       </c>
       <c r="B229" s="11"/>
       <c r="C229" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>114</v>
@@ -14395,8 +14396,8 @@
       <c r="J229" s="1">
         <v>1</v>
       </c>
-      <c r="K229" s="9">
-        <v>1</v>
+      <c r="K229" s="1">
+        <v>0</v>
       </c>
       <c r="L229" s="1">
         <v>1</v>
@@ -14420,19 +14421,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="16.2">
+    <row r="230" spans="1:18">
       <c r="A230" s="5">
         <v>226</v>
       </c>
       <c r="B230" s="11"/>
       <c r="C230" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F230" s="2" t="s">
         <v>114</v>
@@ -14449,8 +14450,8 @@
       <c r="J230" s="1">
         <v>1</v>
       </c>
-      <c r="K230" s="1">
-        <v>0</v>
+      <c r="K230" s="9">
+        <v>1</v>
       </c>
       <c r="L230" s="1">
         <v>1</v>
@@ -14474,19 +14475,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="16.2">
+    <row r="231" spans="1:18">
       <c r="A231" s="5">
         <v>227</v>
       </c>
       <c r="B231" s="11"/>
       <c r="C231" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F231" s="2" t="s">
         <v>114</v>
@@ -14528,19 +14529,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="16.2">
+    <row r="232" spans="1:18">
       <c r="A232" s="5">
         <v>228</v>
       </c>
       <c r="B232" s="11"/>
       <c r="C232" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F232" s="2" t="s">
         <v>114</v>
@@ -14582,19 +14583,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="16.2">
+    <row r="233" spans="1:18">
       <c r="A233" s="5">
         <v>229</v>
       </c>
       <c r="B233" s="11"/>
       <c r="C233" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F233" s="2" t="s">
         <v>114</v>
@@ -14636,19 +14637,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="16.2">
+    <row r="234" spans="1:18">
       <c r="A234" s="5">
         <v>230</v>
       </c>
       <c r="B234" s="11"/>
       <c r="C234" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F234" s="2" t="s">
         <v>114</v>
@@ -14690,19 +14691,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="16.2">
+    <row r="235" spans="1:18">
       <c r="A235" s="5">
         <v>231</v>
       </c>
       <c r="B235" s="11"/>
       <c r="C235" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F235" s="2" t="s">
         <v>114</v>
@@ -14744,19 +14745,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="16.2">
+    <row r="236" spans="1:18">
       <c r="A236" s="5">
         <v>232</v>
       </c>
       <c r="B236" s="11"/>
       <c r="C236" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F236" s="2" t="s">
         <v>114</v>
@@ -14798,19 +14799,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="16.2">
+    <row r="237" spans="1:18">
       <c r="A237" s="5">
         <v>233</v>
       </c>
       <c r="B237" s="11"/>
       <c r="C237" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F237" s="2" t="s">
         <v>114</v>
@@ -14852,19 +14853,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="16.2">
+    <row r="238" spans="1:18">
       <c r="A238" s="5">
         <v>234</v>
       </c>
       <c r="B238" s="11"/>
       <c r="C238" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F238" s="2" t="s">
         <v>114</v>
@@ -14906,19 +14907,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="16.2">
+    <row r="239" spans="1:18">
       <c r="A239" s="5">
         <v>235</v>
       </c>
       <c r="B239" s="11"/>
       <c r="C239" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F239" s="2" t="s">
         <v>114</v>
@@ -14960,19 +14961,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="16.2">
+    <row r="240" spans="1:18">
       <c r="A240" s="5">
         <v>236</v>
       </c>
       <c r="B240" s="11"/>
       <c r="C240" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>114</v>
@@ -15014,19 +15015,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="16.2">
+    <row r="241" spans="1:18">
       <c r="A241" s="5">
         <v>237</v>
       </c>
       <c r="B241" s="11"/>
       <c r="C241" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>114</v>
@@ -15068,19 +15069,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="16.2">
+    <row r="242" spans="1:18">
       <c r="A242" s="5">
         <v>238</v>
       </c>
       <c r="B242" s="11"/>
       <c r="C242" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>114</v>
@@ -15122,19 +15123,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="16.2">
+    <row r="243" spans="1:18">
       <c r="A243" s="5">
         <v>239</v>
       </c>
       <c r="B243" s="11"/>
       <c r="C243" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F243" s="2" t="s">
         <v>114</v>
@@ -15176,19 +15177,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="16.2">
+    <row r="244" spans="1:18">
       <c r="A244" s="5">
         <v>240</v>
       </c>
       <c r="B244" s="11"/>
       <c r="C244" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F244" s="2" t="s">
         <v>114</v>
@@ -15230,19 +15231,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:18" ht="16.2">
+    <row r="245" spans="1:18">
       <c r="A245" s="5">
         <v>241</v>
       </c>
       <c r="B245" s="11"/>
       <c r="C245" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F245" s="2" t="s">
         <v>114</v>
@@ -15259,8 +15260,8 @@
       <c r="J245" s="1">
         <v>1</v>
       </c>
-      <c r="K245" s="9">
-        <v>1</v>
+      <c r="K245" s="1">
+        <v>0</v>
       </c>
       <c r="L245" s="1">
         <v>1</v>
@@ -15284,19 +15285,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:18" ht="16.2">
+    <row r="246" spans="1:18">
       <c r="A246" s="5">
         <v>242</v>
       </c>
       <c r="B246" s="11"/>
       <c r="C246" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F246" s="2" t="s">
         <v>114</v>
@@ -15313,8 +15314,8 @@
       <c r="J246" s="1">
         <v>1</v>
       </c>
-      <c r="K246" s="1">
-        <v>0</v>
+      <c r="K246" s="9">
+        <v>1</v>
       </c>
       <c r="L246" s="1">
         <v>1</v>
@@ -15338,19 +15339,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:18" ht="16.2">
+    <row r="247" spans="1:18">
       <c r="A247" s="5">
         <v>243</v>
       </c>
       <c r="B247" s="11"/>
       <c r="C247" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F247" s="2" t="s">
         <v>114</v>
@@ -15392,19 +15393,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:18" ht="16.2">
+    <row r="248" spans="1:18">
       <c r="A248" s="5">
         <v>244</v>
       </c>
       <c r="B248" s="11"/>
       <c r="C248" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F248" s="2" t="s">
         <v>114</v>
@@ -15446,19 +15447,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:18" ht="16.2">
+    <row r="249" spans="1:18">
       <c r="A249" s="5">
         <v>245</v>
       </c>
       <c r="B249" s="11"/>
       <c r="C249" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>114</v>
@@ -15500,19 +15501,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:18" ht="16.2">
+    <row r="250" spans="1:18">
       <c r="A250" s="5">
         <v>246</v>
       </c>
       <c r="B250" s="11"/>
       <c r="C250" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F250" s="2" t="s">
         <v>114</v>
@@ -15554,19 +15555,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:18" ht="16.2">
+    <row r="251" spans="1:18">
       <c r="A251" s="5">
         <v>247</v>
       </c>
       <c r="B251" s="11"/>
       <c r="C251" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F251" s="2" t="s">
         <v>114</v>
@@ -15608,19 +15609,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="16.2">
+    <row r="252" spans="1:18">
       <c r="A252" s="5">
         <v>248</v>
       </c>
       <c r="B252" s="11"/>
       <c r="C252" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F252" s="2" t="s">
         <v>114</v>
@@ -15662,19 +15663,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:18" ht="16.2">
+    <row r="253" spans="1:18">
       <c r="A253" s="5">
         <v>249</v>
       </c>
       <c r="B253" s="11"/>
       <c r="C253" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F253" s="2" t="s">
         <v>114</v>
@@ -15716,19 +15717,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:18" ht="16.2">
+    <row r="254" spans="1:18">
       <c r="A254" s="5">
         <v>250</v>
       </c>
       <c r="B254" s="11"/>
       <c r="C254" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F254" s="2" t="s">
         <v>114</v>
@@ -15770,19 +15771,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:18" ht="16.2">
+    <row r="255" spans="1:18">
       <c r="A255" s="5">
         <v>251</v>
       </c>
       <c r="B255" s="11"/>
       <c r="C255" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F255" s="2" t="s">
         <v>114</v>
@@ -15824,19 +15825,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:18" ht="16.2">
+    <row r="256" spans="1:18">
       <c r="A256" s="5">
         <v>252</v>
       </c>
       <c r="B256" s="11"/>
       <c r="C256" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F256" s="2" t="s">
         <v>114</v>
@@ -15878,19 +15879,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:18" ht="16.2">
+    <row r="257" spans="1:18">
       <c r="A257" s="5">
         <v>253</v>
       </c>
       <c r="B257" s="11"/>
       <c r="C257" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F257" s="2" t="s">
         <v>114</v>
@@ -15932,19 +15933,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:18" ht="16.2">
+    <row r="258" spans="1:18">
       <c r="A258" s="5">
         <v>254</v>
       </c>
       <c r="B258" s="11"/>
       <c r="C258" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F258" s="2" t="s">
         <v>114</v>
@@ -15986,19 +15987,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:18" ht="16.2">
+    <row r="259" spans="1:18">
       <c r="A259" s="5">
         <v>255</v>
       </c>
       <c r="B259" s="11"/>
       <c r="C259" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F259" s="2" t="s">
         <v>114</v>
@@ -16040,19 +16041,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:18" ht="16.2">
+    <row r="260" spans="1:18">
       <c r="A260" s="5">
         <v>256</v>
       </c>
       <c r="B260" s="11"/>
       <c r="C260" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F260" s="2" t="s">
         <v>114</v>
@@ -16094,19 +16095,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:18" ht="16.2">
+    <row r="261" spans="1:18">
       <c r="A261" s="5">
         <v>257</v>
       </c>
       <c r="B261" s="11"/>
       <c r="C261" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E261" s="9" t="s">
-        <v>49</v>
+      <c r="E261" s="1" t="s">
+        <v>532</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>114</v>
@@ -16123,8 +16124,8 @@
       <c r="J261" s="1">
         <v>1</v>
       </c>
-      <c r="K261" s="9">
-        <v>1</v>
+      <c r="K261" s="1">
+        <v>0</v>
       </c>
       <c r="L261" s="1">
         <v>1</v>
@@ -16148,18 +16149,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:18" ht="16.2">
+    <row r="262" spans="1:18">
       <c r="A262" s="5">
         <v>258</v>
       </c>
       <c r="B262" s="11"/>
       <c r="C262" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E262" s="1" t="s">
+      <c r="E262" s="9" t="s">
         <v>49</v>
       </c>
       <c r="F262" s="2" t="s">
@@ -16177,8 +16178,8 @@
       <c r="J262" s="1">
         <v>1</v>
       </c>
-      <c r="K262" s="1">
-        <v>0</v>
+      <c r="K262" s="9">
+        <v>1</v>
       </c>
       <c r="L262" s="1">
         <v>1</v>
@@ -16202,13 +16203,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:18" ht="16.2">
+    <row r="263" spans="1:18">
       <c r="A263" s="5">
         <v>259</v>
       </c>
       <c r="B263" s="11"/>
       <c r="C263" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>49</v>
@@ -16256,13 +16257,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:18" ht="16.2">
+    <row r="264" spans="1:18">
       <c r="A264" s="5">
         <v>260</v>
       </c>
       <c r="B264" s="11"/>
       <c r="C264" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>49</v>
@@ -16310,13 +16311,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:18" ht="16.2">
+    <row r="265" spans="1:18">
       <c r="A265" s="5">
         <v>261</v>
       </c>
       <c r="B265" s="11"/>
       <c r="C265" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>49</v>
@@ -16364,13 +16365,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:18" ht="16.2">
+    <row r="266" spans="1:18">
       <c r="A266" s="5">
         <v>262</v>
       </c>
       <c r="B266" s="11"/>
       <c r="C266" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>49</v>
@@ -16418,13 +16419,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:18" ht="16.2">
+    <row r="267" spans="1:18">
       <c r="A267" s="5">
         <v>263</v>
       </c>
       <c r="B267" s="11"/>
       <c r="C267" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>49</v>
@@ -16472,13 +16473,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:18" ht="16.2">
+    <row r="268" spans="1:18">
       <c r="A268" s="5">
         <v>264</v>
       </c>
       <c r="B268" s="11"/>
       <c r="C268" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>49</v>
@@ -16526,13 +16527,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:18" ht="16.2">
+    <row r="269" spans="1:18">
       <c r="A269" s="5">
         <v>265</v>
       </c>
       <c r="B269" s="11"/>
       <c r="C269" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>49</v>
@@ -16580,13 +16581,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:18" ht="16.2">
+    <row r="270" spans="1:18">
       <c r="A270" s="5">
         <v>266</v>
       </c>
       <c r="B270" s="11"/>
       <c r="C270" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>49</v>
@@ -16634,13 +16635,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:18" ht="16.2">
+    <row r="271" spans="1:18">
       <c r="A271" s="5">
         <v>267</v>
       </c>
       <c r="B271" s="11"/>
       <c r="C271" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>49</v>
@@ -16688,13 +16689,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:18" ht="16.2">
+    <row r="272" spans="1:18">
       <c r="A272" s="5">
         <v>268</v>
       </c>
       <c r="B272" s="11"/>
       <c r="C272" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>49</v>
@@ -16742,13 +16743,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:18" ht="16.2">
+    <row r="273" spans="1:18">
       <c r="A273" s="5">
         <v>269</v>
       </c>
       <c r="B273" s="11"/>
       <c r="C273" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>49</v>
@@ -16796,13 +16797,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:18" ht="16.2">
+    <row r="274" spans="1:18">
       <c r="A274" s="5">
         <v>270</v>
       </c>
       <c r="B274" s="11"/>
       <c r="C274" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>49</v>
@@ -16850,13 +16851,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:18" ht="16.2">
+    <row r="275" spans="1:18">
       <c r="A275" s="5">
         <v>271</v>
       </c>
       <c r="B275" s="11"/>
       <c r="C275" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>49</v>
@@ -16904,13 +16905,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:18" ht="16.2">
+    <row r="276" spans="1:18">
       <c r="A276" s="5">
         <v>272</v>
       </c>
       <c r="B276" s="11"/>
       <c r="C276" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>49</v>
@@ -16958,13 +16959,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:18" ht="16.2">
+    <row r="277" spans="1:18">
       <c r="A277" s="5">
         <v>273</v>
       </c>
       <c r="B277" s="11"/>
-      <c r="C277" s="9" t="s">
-        <v>49</v>
+      <c r="C277" s="1" t="s">
+        <v>311</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>49</v>
@@ -16984,14 +16985,14 @@
       <c r="I277" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="J277" s="9">
-        <v>0</v>
+      <c r="J277" s="1">
+        <v>1</v>
       </c>
       <c r="K277" s="1">
         <v>0</v>
       </c>
-      <c r="L277" s="9">
-        <v>0</v>
+      <c r="L277" s="1">
+        <v>1</v>
       </c>
       <c r="M277" s="7" t="s">
         <v>141</v>
@@ -17012,12 +17013,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:18" ht="16.2">
+    <row r="278" spans="1:18">
       <c r="A278" s="5">
         <v>274</v>
       </c>
       <c r="B278" s="11"/>
-      <c r="C278" s="1" t="s">
+      <c r="C278" s="9" t="s">
         <v>49</v>
       </c>
       <c r="D278" s="2" t="s">
@@ -17038,13 +17039,13 @@
       <c r="I278" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="J278" s="1">
+      <c r="J278" s="9">
         <v>0</v>
       </c>
       <c r="K278" s="1">
         <v>0</v>
       </c>
-      <c r="L278" s="1">
+      <c r="L278" s="9">
         <v>0</v>
       </c>
       <c r="M278" s="7" t="s">
@@ -17066,7 +17067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:18" ht="16.2">
+    <row r="279" spans="1:18">
       <c r="A279" s="5">
         <v>275</v>
       </c>
@@ -17120,7 +17121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:18" ht="16.2">
+    <row r="280" spans="1:18">
       <c r="A280" s="5">
         <v>276</v>
       </c>
@@ -17174,7 +17175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:18" ht="16.2">
+    <row r="281" spans="1:18">
       <c r="A281" s="5">
         <v>277</v>
       </c>
@@ -17228,7 +17229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:18" ht="16.2">
+    <row r="282" spans="1:18">
       <c r="A282" s="5">
         <v>278</v>
       </c>
@@ -17282,7 +17283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:18" ht="16.2">
+    <row r="283" spans="1:18">
       <c r="A283" s="5">
         <v>279</v>
       </c>
@@ -17336,7 +17337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:18" ht="16.2">
+    <row r="284" spans="1:18">
       <c r="A284" s="5">
         <v>280</v>
       </c>
@@ -17390,7 +17391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:18" ht="16.2">
+    <row r="285" spans="1:18">
       <c r="A285" s="5">
         <v>281</v>
       </c>
@@ -17444,7 +17445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:18" ht="16.2">
+    <row r="286" spans="1:18">
       <c r="A286" s="5">
         <v>282</v>
       </c>
@@ -17498,7 +17499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:18" ht="16.2">
+    <row r="287" spans="1:18">
       <c r="A287" s="5">
         <v>283</v>
       </c>
@@ -17552,7 +17553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:18" ht="16.2">
+    <row r="288" spans="1:18">
       <c r="A288" s="5">
         <v>284</v>
       </c>
@@ -17606,7 +17607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:18" ht="16.2">
+    <row r="289" spans="1:18">
       <c r="A289" s="5">
         <v>285</v>
       </c>
@@ -17660,7 +17661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:18" ht="16.2">
+    <row r="290" spans="1:18">
       <c r="A290" s="5">
         <v>286</v>
       </c>
@@ -17714,7 +17715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:18" ht="16.2">
+    <row r="291" spans="1:18">
       <c r="A291" s="5">
         <v>287</v>
       </c>
@@ -17768,7 +17769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:18" ht="16.2">
+    <row r="292" spans="1:18">
       <c r="A292" s="5">
         <v>288</v>
       </c>
@@ -17822,10 +17823,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:18" ht="16.2">
+    <row r="293" spans="1:18">
       <c r="A293" s="5">
         <v>289</v>
       </c>
+      <c r="B293" s="11"/>
       <c r="C293" s="1" t="s">
         <v>49</v>
       </c>
@@ -17875,7 +17877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:18" ht="16.2">
+    <row r="294" spans="1:18">
       <c r="A294" s="5">
         <v>290</v>
       </c>
@@ -17928,7 +17930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:18" ht="16.2">
+    <row r="295" spans="1:18">
       <c r="A295" s="5">
         <v>291</v>
       </c>
@@ -17981,7 +17983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:18" ht="16.2">
+    <row r="296" spans="1:18">
       <c r="A296" s="5">
         <v>292</v>
       </c>
@@ -18034,7 +18036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:18" ht="16.2">
+    <row r="297" spans="1:18">
       <c r="A297" s="5">
         <v>293</v>
       </c>
@@ -18087,7 +18089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:18" ht="16.2">
+    <row r="298" spans="1:18">
       <c r="A298" s="5">
         <v>294</v>
       </c>
@@ -18140,7 +18142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:18" ht="16.2">
+    <row r="299" spans="1:18">
       <c r="A299" s="5">
         <v>295</v>
       </c>
@@ -18193,7 +18195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:18" ht="16.2">
+    <row r="300" spans="1:18">
       <c r="A300" s="5">
         <v>296</v>
       </c>
@@ -18246,7 +18248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:18" ht="16.2">
+    <row r="301" spans="1:18">
       <c r="A301" s="5">
         <v>297</v>
       </c>
@@ -18299,7 +18301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:18" ht="16.2">
+    <row r="302" spans="1:18">
       <c r="A302" s="5">
         <v>298</v>
       </c>
@@ -18352,7 +18354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:18" ht="16.2">
+    <row r="303" spans="1:18">
       <c r="A303" s="5">
         <v>299</v>
       </c>
@@ -18405,7 +18407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:18" ht="16.2">
+    <row r="304" spans="1:18">
       <c r="A304" s="5">
         <v>300</v>
       </c>
@@ -18458,7 +18460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:18" ht="16.2">
+    <row r="305" spans="1:18">
       <c r="A305" s="5">
         <v>301</v>
       </c>
@@ -18511,7 +18513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:18" ht="16.2">
+    <row r="306" spans="1:18">
       <c r="A306" s="5">
         <v>302</v>
       </c>
@@ -18564,7 +18566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:18" ht="16.2">
+    <row r="307" spans="1:18">
       <c r="A307" s="5">
         <v>303</v>
       </c>
@@ -18617,7 +18619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:18" ht="16.2">
+    <row r="308" spans="1:18">
       <c r="A308" s="5">
         <v>304</v>
       </c>
@@ -18651,8 +18653,8 @@
       <c r="L308" s="1">
         <v>0</v>
       </c>
-      <c r="M308" s="10" t="s">
-        <v>329</v>
+      <c r="M308" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="N308" s="1">
         <v>0</v>
@@ -18670,33 +18672,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:18" ht="16.2">
+    <row r="309" spans="1:18">
       <c r="A309" s="5">
         <v>305</v>
       </c>
-      <c r="B309" s="11" t="s">
-        <v>331</v>
-      </c>
       <c r="C309" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D309" s="8" t="s">
-        <v>317</v>
+      <c r="D309" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>328</v>
+        <v>114</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="H309" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I309" s="9">
-        <v>11</v>
+        <v>114</v>
+      </c>
+      <c r="H309" s="6">
+        <v>11</v>
+      </c>
+      <c r="I309" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="J309" s="1">
         <v>0</v>
@@ -18707,35 +18706,37 @@
       <c r="L309" s="1">
         <v>0</v>
       </c>
-      <c r="M309" s="7" t="s">
+      <c r="M309" s="10" t="s">
         <v>329</v>
       </c>
       <c r="N309" s="1">
         <v>0</v>
       </c>
-      <c r="O309" s="9">
-        <v>1</v>
-      </c>
-      <c r="P309" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q309" s="9">
-        <v>1</v>
+      <c r="O309" s="1">
+        <v>0</v>
+      </c>
+      <c r="P309" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q309" s="1">
+        <v>0</v>
       </c>
       <c r="R309" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:18" ht="16.2">
+    <row r="310" spans="1:18">
       <c r="A310" s="5">
         <v>306</v>
       </c>
-      <c r="B310" s="11"/>
+      <c r="B310" s="11" t="s">
+        <v>331</v>
+      </c>
       <c r="C310" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D310" s="2" t="s">
-        <v>312</v>
+      <c r="D310" s="8" t="s">
+        <v>317</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>49</v>
@@ -18746,10 +18747,10 @@
       <c r="G310" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="H310" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="I310" s="1">
+      <c r="H310" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="I310" s="9">
         <v>11</v>
       </c>
       <c r="J310" s="1">
@@ -18767,20 +18768,20 @@
       <c r="N310" s="1">
         <v>0</v>
       </c>
-      <c r="O310" s="1">
-        <v>1</v>
-      </c>
-      <c r="P310" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q310" s="1">
+      <c r="O310" s="9">
+        <v>1</v>
+      </c>
+      <c r="P310" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q310" s="9">
         <v>1</v>
       </c>
       <c r="R310" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:18" ht="16.2">
+    <row r="311" spans="1:18">
       <c r="A311" s="5">
         <v>307</v>
       </c>
@@ -18789,7 +18790,7 @@
         <v>49</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>49</v>
@@ -18834,7 +18835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:18" ht="16.2">
+    <row r="312" spans="1:18">
       <c r="A312" s="5">
         <v>308</v>
       </c>
@@ -18843,7 +18844,7 @@
         <v>49</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>49</v>
@@ -18888,7 +18889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:18" ht="16.2">
+    <row r="313" spans="1:18">
       <c r="A313" s="5">
         <v>309</v>
       </c>
@@ -18897,7 +18898,7 @@
         <v>49</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>49</v>
@@ -18942,7 +18943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:18" ht="16.2">
+    <row r="314" spans="1:18">
       <c r="A314" s="5">
         <v>310</v>
       </c>
@@ -18951,7 +18952,7 @@
         <v>49</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>49</v>
@@ -18996,7 +18997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:18" ht="16.2">
+    <row r="315" spans="1:18">
       <c r="A315" s="5">
         <v>311</v>
       </c>
@@ -19005,7 +19006,7 @@
         <v>49</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>49</v>
@@ -19050,7 +19051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:18" ht="16.2">
+    <row r="316" spans="1:18">
       <c r="A316" s="5">
         <v>312</v>
       </c>
@@ -19059,7 +19060,7 @@
         <v>49</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>49</v>
@@ -19104,7 +19105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:18" ht="16.2">
+    <row r="317" spans="1:18">
       <c r="A317" s="5">
         <v>313</v>
       </c>
@@ -19113,7 +19114,7 @@
         <v>49</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>49</v>
@@ -19158,7 +19159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:18" ht="16.2">
+    <row r="318" spans="1:18">
       <c r="A318" s="5">
         <v>314</v>
       </c>
@@ -19167,7 +19168,7 @@
         <v>49</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>49</v>
@@ -19212,7 +19213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:18" ht="16.2">
+    <row r="319" spans="1:18">
       <c r="A319" s="5">
         <v>315</v>
       </c>
@@ -19221,7 +19222,7 @@
         <v>49</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>49</v>
@@ -19266,7 +19267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:18" ht="16.2">
+    <row r="320" spans="1:18">
       <c r="A320" s="5">
         <v>316</v>
       </c>
@@ -19275,7 +19276,7 @@
         <v>49</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>49</v>
@@ -19320,7 +19321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:18" ht="16.2">
+    <row r="321" spans="1:18">
       <c r="A321" s="5">
         <v>317</v>
       </c>
@@ -19329,7 +19330,7 @@
         <v>49</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>49</v>
@@ -19374,7 +19375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:18" ht="16.2">
+    <row r="322" spans="1:18">
       <c r="A322" s="5">
         <v>318</v>
       </c>
@@ -19383,7 +19384,7 @@
         <v>49</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>49</v>
@@ -19428,7 +19429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:18" ht="16.2">
+    <row r="323" spans="1:18">
       <c r="A323" s="5">
         <v>319</v>
       </c>
@@ -19437,7 +19438,7 @@
         <v>49</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>49</v>
@@ -19482,7 +19483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:18" ht="16.2">
+    <row r="324" spans="1:18">
       <c r="A324" s="5">
         <v>320</v>
       </c>
@@ -19491,9 +19492,9 @@
         <v>49</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E324" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E324" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F324" s="2" t="s">
@@ -19517,8 +19518,8 @@
       <c r="L324" s="1">
         <v>0</v>
       </c>
-      <c r="M324" s="10" t="s">
-        <v>95</v>
+      <c r="M324" s="7" t="s">
+        <v>329</v>
       </c>
       <c r="N324" s="1">
         <v>0</v>
@@ -19536,30 +19537,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:18" ht="16.2">
+    <row r="325" spans="1:18">
       <c r="A325" s="5">
         <v>321</v>
       </c>
+      <c r="B325" s="11"/>
       <c r="C325" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D325" s="8" t="s">
-        <v>49</v>
+      <c r="D325" s="2" t="s">
+        <v>327</v>
       </c>
       <c r="E325" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F325" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="G325" s="8" t="s">
-        <v>114</v>
+      <c r="F325" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="G325" s="2" t="s">
+        <v>328</v>
       </c>
       <c r="H325" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="I325" s="7" t="s">
-        <v>95</v>
+      <c r="I325" s="1">
+        <v>11</v>
       </c>
       <c r="J325" s="1">
         <v>0</v>
@@ -19570,7 +19572,7 @@
       <c r="L325" s="1">
         <v>0</v>
       </c>
-      <c r="M325" s="7" t="s">
+      <c r="M325" s="10" t="s">
         <v>95</v>
       </c>
       <c r="N325" s="1">
@@ -19589,26 +19591,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:18" ht="16.2">
+    <row r="326" spans="1:18">
       <c r="A326" s="5">
         <v>322</v>
       </c>
-      <c r="B326" s="5" t="s">
-        <v>332</v>
-      </c>
       <c r="C326" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D326" s="12" t="s">
+      <c r="D326" s="8" t="s">
         <v>49</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F326" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="G326" s="12" t="s">
+      <c r="F326" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G326" s="8" t="s">
         <v>114</v>
       </c>
       <c r="H326" s="7" t="s">
@@ -19632,260 +19631,311 @@
       <c r="N326" s="1">
         <v>0</v>
       </c>
-      <c r="O326" s="9">
-        <v>0</v>
-      </c>
-      <c r="P326" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q326" s="9">
-        <v>0</v>
-      </c>
-      <c r="R326" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="327" spans="1:18" ht="16.2">
+      <c r="O326" s="1">
+        <v>1</v>
+      </c>
+      <c r="P326" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q326" s="1">
+        <v>1</v>
+      </c>
+      <c r="R326" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:18">
       <c r="A327" s="5">
         <v>323</v>
       </c>
-    </row>
-    <row r="328" spans="1:18" ht="16.2">
+      <c r="B327" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D327" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E327" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F327" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G327" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H327" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="I327" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="J327" s="1">
+        <v>0</v>
+      </c>
+      <c r="K327" s="1">
+        <v>0</v>
+      </c>
+      <c r="L327" s="1">
+        <v>0</v>
+      </c>
+      <c r="M327" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="N327" s="1">
+        <v>0</v>
+      </c>
+      <c r="O327" s="9">
+        <v>0</v>
+      </c>
+      <c r="P327" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q327" s="9">
+        <v>0</v>
+      </c>
+      <c r="R327" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:18">
       <c r="A328" s="5">
         <v>324</v>
       </c>
     </row>
-    <row r="329" spans="1:18" ht="16.2">
+    <row r="329" spans="1:18">
       <c r="A329" s="5">
         <v>325</v>
       </c>
     </row>
-    <row r="330" spans="1:18" ht="16.2">
+    <row r="330" spans="1:18">
       <c r="A330" s="5">
         <v>326</v>
       </c>
     </row>
-    <row r="331" spans="1:18" ht="16.2">
+    <row r="331" spans="1:18">
       <c r="A331" s="5">
         <v>327</v>
       </c>
     </row>
-    <row r="332" spans="1:18" ht="16.2">
+    <row r="332" spans="1:18">
       <c r="A332" s="5">
         <v>328</v>
       </c>
     </row>
-    <row r="333" spans="1:18" ht="16.2">
+    <row r="333" spans="1:18">
       <c r="A333" s="5">
         <v>329</v>
       </c>
     </row>
-    <row r="334" spans="1:18" ht="16.2">
+    <row r="334" spans="1:18">
       <c r="A334" s="5">
         <v>330</v>
       </c>
     </row>
-    <row r="335" spans="1:18" ht="16.2">
+    <row r="335" spans="1:18">
       <c r="A335" s="5">
         <v>331</v>
       </c>
     </row>
-    <row r="336" spans="1:18" ht="16.2">
+    <row r="336" spans="1:18">
       <c r="A336" s="5">
         <v>332</v>
       </c>
     </row>
-    <row r="337" spans="1:1" ht="16.2">
+    <row r="337" spans="1:1">
       <c r="A337" s="5">
         <v>333</v>
       </c>
     </row>
-    <row r="338" spans="1:1" ht="16.2">
+    <row r="338" spans="1:1">
       <c r="A338" s="5">
         <v>334</v>
       </c>
     </row>
-    <row r="339" spans="1:1" ht="16.2">
+    <row r="339" spans="1:1">
       <c r="A339" s="5">
         <v>335</v>
       </c>
     </row>
-    <row r="340" spans="1:1" ht="16.2">
+    <row r="340" spans="1:1">
       <c r="A340" s="5">
         <v>336</v>
       </c>
     </row>
-    <row r="341" spans="1:1" ht="16.2">
+    <row r="341" spans="1:1">
       <c r="A341" s="5">
         <v>337</v>
       </c>
     </row>
-    <row r="342" spans="1:1" ht="16.2">
+    <row r="342" spans="1:1">
       <c r="A342" s="5">
         <v>338</v>
       </c>
     </row>
-    <row r="343" spans="1:1" ht="16.2">
+    <row r="343" spans="1:1">
       <c r="A343" s="5">
         <v>339</v>
       </c>
     </row>
-    <row r="344" spans="1:1" ht="16.2">
+    <row r="344" spans="1:1">
       <c r="A344" s="5">
         <v>340</v>
       </c>
     </row>
-    <row r="345" spans="1:1" ht="16.2">
+    <row r="345" spans="1:1">
       <c r="A345" s="5">
         <v>341</v>
       </c>
     </row>
-    <row r="346" spans="1:1" ht="16.2">
+    <row r="346" spans="1:1">
       <c r="A346" s="5">
         <v>342</v>
       </c>
     </row>
-    <row r="347" spans="1:1" ht="16.2">
+    <row r="347" spans="1:1">
       <c r="A347" s="5">
         <v>343</v>
       </c>
     </row>
-    <row r="348" spans="1:1" ht="16.2">
+    <row r="348" spans="1:1">
       <c r="A348" s="5">
         <v>344</v>
       </c>
     </row>
-    <row r="349" spans="1:1" ht="16.2">
+    <row r="349" spans="1:1">
       <c r="A349" s="5">
         <v>345</v>
       </c>
     </row>
-    <row r="350" spans="1:1" ht="16.2">
+    <row r="350" spans="1:1">
       <c r="A350" s="5">
         <v>346</v>
       </c>
     </row>
-    <row r="351" spans="1:1" ht="16.2">
+    <row r="351" spans="1:1">
       <c r="A351" s="5">
         <v>347</v>
       </c>
     </row>
-    <row r="352" spans="1:1" ht="16.2">
+    <row r="352" spans="1:1">
       <c r="A352" s="5">
         <v>348</v>
       </c>
     </row>
-    <row r="353" spans="1:1" ht="16.2">
+    <row r="353" spans="1:1">
       <c r="A353" s="5">
         <v>349</v>
       </c>
     </row>
-    <row r="354" spans="1:1" ht="16.2">
+    <row r="354" spans="1:1">
       <c r="A354" s="5">
         <v>350</v>
       </c>
     </row>
-    <row r="355" spans="1:1" ht="16.2">
+    <row r="355" spans="1:1">
       <c r="A355" s="5">
         <v>351</v>
       </c>
     </row>
-    <row r="356" spans="1:1" ht="16.2">
+    <row r="356" spans="1:1">
       <c r="A356" s="5">
         <v>352</v>
       </c>
     </row>
-    <row r="357" spans="1:1" ht="16.2">
+    <row r="357" spans="1:1">
       <c r="A357" s="5">
         <v>353</v>
       </c>
     </row>
-    <row r="358" spans="1:1" ht="16.2">
+    <row r="358" spans="1:1">
       <c r="A358" s="5">
         <v>354</v>
       </c>
     </row>
-    <row r="359" spans="1:1" ht="16.2">
+    <row r="359" spans="1:1">
       <c r="A359" s="5">
         <v>355</v>
       </c>
     </row>
-    <row r="360" spans="1:1" ht="16.2">
+    <row r="360" spans="1:1">
       <c r="A360" s="5">
         <v>356</v>
       </c>
     </row>
-    <row r="361" spans="1:1" ht="16.2">
+    <row r="361" spans="1:1">
       <c r="A361" s="5">
         <v>357</v>
       </c>
     </row>
-    <row r="362" spans="1:1" ht="16.2">
+    <row r="362" spans="1:1">
       <c r="A362" s="5">
         <v>358</v>
       </c>
     </row>
-    <row r="363" spans="1:1" ht="16.2">
+    <row r="363" spans="1:1">
       <c r="A363" s="5">
         <v>359</v>
       </c>
     </row>
-    <row r="364" spans="1:1" ht="16.2">
+    <row r="364" spans="1:1">
       <c r="A364" s="5">
         <v>360</v>
       </c>
     </row>
-    <row r="365" spans="1:1" ht="16.2">
+    <row r="365" spans="1:1">
       <c r="A365" s="5">
         <v>361</v>
       </c>
     </row>
-    <row r="366" spans="1:1" ht="16.2">
+    <row r="366" spans="1:1">
       <c r="A366" s="5">
         <v>362</v>
       </c>
     </row>
-    <row r="367" spans="1:1" ht="16.2">
+    <row r="367" spans="1:1">
       <c r="A367" s="5">
         <v>363</v>
       </c>
     </row>
-    <row r="368" spans="1:1" ht="16.2">
+    <row r="368" spans="1:1">
       <c r="A368" s="5">
         <v>364</v>
       </c>
     </row>
-    <row r="369" spans="1:1" ht="16.2">
+    <row r="369" spans="1:1">
       <c r="A369" s="5">
         <v>365</v>
       </c>
     </row>
-    <row r="370" spans="1:1" ht="16.2">
+    <row r="370" spans="1:1">
       <c r="A370" s="5">
         <v>366</v>
       </c>
     </row>
-    <row r="371" spans="1:1" ht="16.2">
+    <row r="371" spans="1:1">
       <c r="A371" s="5">
         <v>367</v>
       </c>
     </row>
-    <row r="372" spans="1:1" ht="16.2">
+    <row r="372" spans="1:1">
       <c r="A372" s="5">
         <v>368</v>
       </c>
     </row>
-    <row r="373" spans="1:1" ht="16.2">
+    <row r="373" spans="1:1">
       <c r="A373" s="5">
         <v>369</v>
       </c>
     </row>
-    <row r="374" spans="1:1" ht="16.2">
+    <row r="374" spans="1:1">
       <c r="A374" s="5">
         <v>370</v>
       </c>
     </row>
-    <row r="375" spans="1:1" ht="16.2">
+    <row r="375" spans="1:1">
       <c r="A375" s="5">
         <v>371</v>
       </c>
@@ -19894,9 +19944,9 @@
   <mergeCells count="5">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B19"/>
-    <mergeCell ref="B20:B292"/>
-    <mergeCell ref="B309:B324"/>
+    <mergeCell ref="B6:B20"/>
+    <mergeCell ref="B21:B293"/>
+    <mergeCell ref="B310:B325"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19907,13 +19957,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{777FEA12-A55F-4DDB-9244-AE2EF0C1A174}">
   <dimension ref="A1:Q19"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" customWidth="1"/>
-    <col min="2" max="6" width="14.81640625" customWidth="1"/>
-    <col min="7" max="13" width="16.81640625" customWidth="1"/>
-    <col min="14" max="17" width="12.81640625" customWidth="1"/>
-    <col min="18" max="18" width="14.1796875" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" customWidth="1"/>
+    <col min="2" max="6" width="14.77734375" customWidth="1"/>
+    <col min="7" max="13" width="16.77734375" customWidth="1"/>
+    <col min="14" max="17" width="12.77734375" customWidth="1"/>
+    <col min="18" max="18" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -19922,7 +19972,7 @@
     <row r="2" spans="1:17">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:17" ht="20.399999999999999">
+    <row r="3" spans="1:17" ht="21">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -19975,7 +20025,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="20.399999999999999">
+    <row r="4" spans="1:17" ht="21">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -20028,7 +20078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="20.399999999999999">
+    <row r="5" spans="1:17" ht="21">
       <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
@@ -20143,7 +20193,7 @@
     <row r="9" spans="1:17">
       <c r="A9" s="1"/>
     </row>
-    <row r="10" spans="1:17" ht="16.2">
+    <row r="10" spans="1:17">
       <c r="A10" s="1"/>
       <c r="B10" s="5" t="s">
         <v>45</v>
